--- a/version2.xlsx
+++ b/version2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier3/Library/CloudStorage/Dropbox/Git/psychometrics_syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88004ADD-59A7-374D-99A7-3ED0FB9F9F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EFC8FC-CF4F-B541-92AD-548360111C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17780" yWindow="3300" windowWidth="32480" windowHeight="24580" xr2:uid="{A5CC9316-BAE9-7D43-9646-2943D22AD10C}"/>
+    <workbookView xWindow="-30260" yWindow="540" windowWidth="32480" windowHeight="21100" xr2:uid="{A5CC9316-BAE9-7D43-9646-2943D22AD10C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -265,16 +265,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PCの基本的理解</t>
-    <rPh sb="3" eb="6">
-      <t xml:space="preserve">キホンテキ </t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t xml:space="preserve">リカイ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>統計環境Rの導入</t>
     <rPh sb="0" eb="4">
       <t xml:space="preserve">トウケイカンキョウ </t>
@@ -452,13 +442,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>尤度</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">ユウド </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>回帰分析の確率モデル</t>
     <rPh sb="0" eb="4">
       <t xml:space="preserve">カイキブンセキノ </t>
@@ -508,6 +491,26 @@
     <t>第二版</t>
     <rPh sb="0" eb="3">
       <t xml:space="preserve">ダイニハン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電子計算機の基礎</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">デンシケイサンキ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">キソ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>尤度と確率モデル</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ユウド </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">カクリツ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -555,11 +558,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -905,11 +905,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>55</v>
+      <c r="B1" t="s">
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -942,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -953,7 +953,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -964,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -972,10 +972,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -986,7 +986,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -997,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1008,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1019,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1041,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1085,7 +1085,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1096,7 +1096,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1118,7 +1118,7 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1129,7 +1129,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1140,7 +1140,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1151,7 +1151,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1162,7 +1162,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1173,7 +1173,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1184,7 +1184,7 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1195,7 +1195,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1206,7 +1206,7 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1217,7 +1217,7 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1228,7 +1228,7 @@
         <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1239,7 +1239,7 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
